--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.37612789887898</v>
+        <v>2.498620783567835</v>
       </c>
       <c r="D2" t="n">
-        <v>20.14949916168624</v>
+        <v>3.274293613774015</v>
       </c>
       <c r="E2" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F2" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.61311564086142</v>
+        <v>6.762131291639981</v>
       </c>
       <c r="D3" t="n">
-        <v>39.50929727615556</v>
+        <v>6.420260807375279</v>
       </c>
       <c r="E3" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F3" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.09795392604057</v>
+        <v>4.565917512981593</v>
       </c>
       <c r="D4" t="n">
-        <v>16.23774651488767</v>
+        <v>2.638633808669246</v>
       </c>
       <c r="E4" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F4" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.30654523364158</v>
+        <v>6.062313600466757</v>
       </c>
       <c r="D5" t="n">
-        <v>23.90897835226704</v>
+        <v>3.885208982243394</v>
       </c>
       <c r="E5" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F5" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.51734246791594</v>
+        <v>1.87156815103634</v>
       </c>
       <c r="D6" t="n">
-        <v>4.072895417618377</v>
+        <v>0.6618455053629864</v>
       </c>
       <c r="E6" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F6" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.2941111288911</v>
+        <v>8.335293058444805</v>
       </c>
       <c r="D7" t="n">
-        <v>47.64983900236016</v>
+        <v>7.743098837883526</v>
       </c>
       <c r="E7" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F7" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.729361873545</v>
+        <v>7.268521304451062</v>
       </c>
       <c r="D8" t="n">
-        <v>44.5167812192652</v>
+        <v>7.233976948130595</v>
       </c>
       <c r="E8" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F8" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.14108613867324</v>
+        <v>6.197926497534401</v>
       </c>
       <c r="D9" t="n">
-        <v>24.05451062941856</v>
+        <v>3.908857977280516</v>
       </c>
       <c r="E9" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F9" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.82348055603641</v>
+        <v>2.571315590355917</v>
       </c>
       <c r="D10" t="n">
-        <v>21.83084796537215</v>
+        <v>3.547512794372975</v>
       </c>
       <c r="E10" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F10" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.55459962627945</v>
+        <v>4.965122439270411</v>
       </c>
       <c r="D11" t="n">
-        <v>12.30779143184575</v>
+        <v>2.000016107674935</v>
       </c>
       <c r="E11" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F11" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.30459567738316</v>
+        <v>2.486996797574763</v>
       </c>
       <c r="D12" t="n">
-        <v>17.73508129516195</v>
+        <v>2.881950710463816</v>
       </c>
       <c r="E12" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F12" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.94698234541318</v>
+        <v>7.141384631129642</v>
       </c>
       <c r="D13" t="n">
-        <v>41.71935973212272</v>
+        <v>6.779395956469942</v>
       </c>
       <c r="E13" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F13" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.35027212823781</v>
+        <v>5.744419220838645</v>
       </c>
       <c r="D14" t="n">
-        <v>34.83682935757989</v>
+        <v>5.660984770606733</v>
       </c>
       <c r="E14" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F14" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.7261630817718</v>
+        <v>4.180501500787918</v>
       </c>
       <c r="D15" t="n">
-        <v>21.52043160113897</v>
+        <v>3.497070135185082</v>
       </c>
       <c r="E15" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F15" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.30366942575356</v>
+        <v>6.061846281684954</v>
       </c>
       <c r="D16" t="n">
-        <v>25.82475330034056</v>
+        <v>4.196522411305342</v>
       </c>
       <c r="E16" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F16" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.42917926230178</v>
+        <v>4.13224163012404</v>
       </c>
       <c r="D17" t="n">
-        <v>24.60937090970374</v>
+        <v>3.999022772826858</v>
       </c>
       <c r="E17" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F17" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>31.43968199986837</v>
+        <v>5.10894832497861</v>
       </c>
       <c r="D18" t="n">
-        <v>29.38977032769813</v>
+        <v>4.775837678250947</v>
       </c>
       <c r="E18" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F18" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>35.07386380811093</v>
+        <v>5.699502868818026</v>
       </c>
       <c r="D19" t="n">
-        <v>23.63874818306186</v>
+        <v>3.841296579747553</v>
       </c>
       <c r="E19" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F19" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>42.96901229321028</v>
+        <v>6.98246449764667</v>
       </c>
       <c r="D20" t="n">
-        <v>27.53452359996309</v>
+        <v>4.474360084994003</v>
       </c>
       <c r="E20" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F20" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>29.28786973797759</v>
+        <v>4.759278832421358</v>
       </c>
       <c r="D21" t="n">
-        <v>16.27137915930725</v>
+        <v>2.644099113387428</v>
       </c>
       <c r="E21" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F21" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>35.62651266695973</v>
+        <v>5.789308308380956</v>
       </c>
       <c r="D22" t="n">
-        <v>23.97817359234443</v>
+        <v>3.896453208755969</v>
       </c>
       <c r="E22" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F22" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>25.95020027221977</v>
+        <v>4.216907544235713</v>
       </c>
       <c r="D23" t="n">
-        <v>24.46286889446657</v>
+        <v>3.975216195350818</v>
       </c>
       <c r="E23" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F23" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>38.71023315373183</v>
+        <v>6.290412887481422</v>
       </c>
       <c r="D24" t="n">
-        <v>4.499026917957568</v>
+        <v>0.7310918741681048</v>
       </c>
       <c r="E24" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F24" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>43.65208939174329</v>
+        <v>7.093464526158285</v>
       </c>
       <c r="D25" t="n">
-        <v>42.83264107325371</v>
+        <v>6.960304174403729</v>
       </c>
       <c r="E25" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F25" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>15.83356365896115</v>
+        <v>2.572954094581186</v>
       </c>
       <c r="D26" t="n">
-        <v>16.18824357641715</v>
+        <v>2.630589581167787</v>
       </c>
       <c r="E26" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F26" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>12.43317702907505</v>
+        <v>2.020391267224695</v>
       </c>
       <c r="D27" t="n">
-        <v>11.62781389845374</v>
+        <v>1.889519758498732</v>
       </c>
       <c r="E27" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F27" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>59.30658586806125</v>
+        <v>9.637320203559954</v>
       </c>
       <c r="D28" t="n">
-        <v>25.35847923547078</v>
+        <v>4.120752875764001</v>
       </c>
       <c r="E28" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F28" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>17.80140874883</v>
+        <v>2.892728921684875</v>
       </c>
       <c r="D29" t="n">
-        <v>15.73738336623144</v>
+        <v>2.55732479701261</v>
       </c>
       <c r="E29" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F29" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>38.39731719114227</v>
+        <v>6.23956404356062</v>
       </c>
       <c r="D30" t="n">
-        <v>13.02219404483957</v>
+        <v>2.116106532286431</v>
       </c>
       <c r="E30" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F30" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>47.61893927301025</v>
+        <v>7.738077631864166</v>
       </c>
       <c r="D31" t="n">
-        <v>3.566389743489783</v>
+        <v>0.5795383333170898</v>
       </c>
       <c r="E31" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F31" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>7.900179431520669</v>
+        <v>1.283779157622109</v>
       </c>
       <c r="D32" t="n">
-        <v>9.472727330871217</v>
+        <v>1.539318191266573</v>
       </c>
       <c r="E32" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F32" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>18.67189350319978</v>
+        <v>3.034182694269965</v>
       </c>
       <c r="D33" t="n">
-        <v>20.95461105957219</v>
+        <v>3.40512429718048</v>
       </c>
       <c r="E33" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F33" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>18.31634544202828</v>
+        <v>2.976406134329596</v>
       </c>
       <c r="D34" t="n">
-        <v>20.78284432675516</v>
+        <v>3.377212203097713</v>
       </c>
       <c r="E34" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F34" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>20.70469549976535</v>
+        <v>3.364513018711869</v>
       </c>
       <c r="D35" t="n">
-        <v>20.25382467349964</v>
+        <v>3.291246509443692</v>
       </c>
       <c r="E35" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F35" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>36.64887507350402</v>
+        <v>5.955442199444404</v>
       </c>
       <c r="D36" t="n">
-        <v>8.490999826104398</v>
+        <v>1.379787471741965</v>
       </c>
       <c r="E36" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F36" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>43.72981061579485</v>
+        <v>7.106094225066664</v>
       </c>
       <c r="D37" t="n">
-        <v>1.343436528903089</v>
+        <v>0.218308435946752</v>
       </c>
       <c r="E37" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F37" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>18.87924281269317</v>
+        <v>3.06787695706264</v>
       </c>
       <c r="D38" t="n">
-        <v>20.42719347793296</v>
+        <v>3.319418940164106</v>
       </c>
       <c r="E38" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F38" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>39.30275162358529</v>
+        <v>6.386697138832609</v>
       </c>
       <c r="D39" t="n">
-        <v>38.58808737671531</v>
+        <v>6.270564198716237</v>
       </c>
       <c r="E39" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F39" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>22.77985442030373</v>
+        <v>3.701726343299356</v>
       </c>
       <c r="D40" t="n">
-        <v>25.16088572046586</v>
+        <v>4.088643929575703</v>
       </c>
       <c r="E40" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F40" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>30.41983715013504</v>
+        <v>4.943223536896943</v>
       </c>
       <c r="D41" t="n">
-        <v>30.77814462828679</v>
+        <v>5.001448502096602</v>
       </c>
       <c r="E41" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F41" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>48.54664508884146</v>
+        <v>7.888829826936737</v>
       </c>
       <c r="D42" t="n">
-        <v>24.39781527429304</v>
+        <v>3.964644982072619</v>
       </c>
       <c r="E42" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F42" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>42.96449784359448</v>
+        <v>6.981730899584103</v>
       </c>
       <c r="D43" t="n">
-        <v>44.58409156664024</v>
+        <v>7.244914879579039</v>
       </c>
       <c r="E43" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F43" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>45.94974940329102</v>
+        <v>7.466834278034791</v>
       </c>
       <c r="D44" t="n">
-        <v>40.23262327258911</v>
+        <v>6.537801281795731</v>
       </c>
       <c r="E44" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F44" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>50.77005528949776</v>
+        <v>8.250133984543387</v>
       </c>
       <c r="D45" t="n">
-        <v>52.27396738609189</v>
+        <v>8.494519700239932</v>
       </c>
       <c r="E45" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F45" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>82.20943310318981</v>
+        <v>13.35903287926834</v>
       </c>
       <c r="D46" t="n">
-        <v>82.05126215157651</v>
+        <v>13.33333009963118</v>
       </c>
       <c r="E46" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F46" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>102.9143809107924</v>
+        <v>16.72358689800376</v>
       </c>
       <c r="D47" t="n">
-        <v>62.93962263673615</v>
+        <v>10.22768867846962</v>
       </c>
       <c r="E47" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F47" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>110.318873297082</v>
+        <v>17.92681691077583</v>
       </c>
       <c r="D48" t="n">
-        <v>70.58970399479692</v>
+        <v>11.4708268991545</v>
       </c>
       <c r="E48" t="n">
-        <v>20.47261622616007</v>
+        <v>3.326800136751012</v>
       </c>
       <c r="F48" t="n">
-        <v>16.852365194763</v>
+        <v>2.738509344148987</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
